--- a/data/Internet.xlsx
+++ b/data/Internet.xlsx
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Customer Name</t>
+          <t>Customer ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Customer Name</t>
+          <t>Customer ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -680,13 +680,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Customer Name</t>
+          <t>Customer ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -900,6 +900,98 @@
         </is>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F8" t="n">
+        <v>33</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>200</v>
+      </c>
+      <c r="C9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" t="n">
+        <v>90</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>90</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>150</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>17</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t>June</t>
         </is>
